--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -65,7 +65,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -114,6 +114,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="007030A0"/>
       </patternFill>
     </fill>
@@ -144,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -201,6 +206,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -568,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -655,7 +663,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>47節</t>
+          <t>49節</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -677,7 +685,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>54頁（推定）</t>
+          <t>56頁（推定）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -820,25 +828,41 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>欠落</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>落ちていたものを令和8年9月16日に追加した</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>欠落</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
           <t>今回の計画素案にない（下記 03 参照）</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>落ちているのは4件です。うち「障がい福祉サービスの体系」と「『障害』と『障がい』の表記について」は追加を推奨します（いずれも1頁以内）。ＳＤＧｓと概要版は村との協議事項、第3章の施策の展開は改定対象外のため現行のままでよいと考えます。詳細は 03_不足分 をご覧ください。</t>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>落ちていた4件のうち2件は令和8年9月16日に追加し（2件）、あわせて用語解説を新設しました。残る2件は、ＳＤＧｓ対応表（今回は見送り）と概要版（仕様書の成果品に含まれておらず契約範囲の確認が必要）です。第3章の施策の展開は改定対象外のため現行のままとしています。詳細は 03_不足分 をご覧ください。</t>
         </is>
       </c>
     </row>
@@ -846,7 +870,7 @@
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
@@ -860,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -872,7 +896,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案の目次（55項目・推定54ページ）</t>
+          <t>計画素案の目次（57項目・推定56ページ）</t>
         </is>
       </c>
     </row>
@@ -1022,40 +1046,40 @@
       <c r="D12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　７　障がい福祉サービスの体系</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>第2章　本村の障がい者の現状</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C14" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　１　人口の推移</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -1065,11 +1089,11 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　２　障がい者手帳の所持者数</t>
+          <t xml:space="preserve">　　１　人口の推移</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
     </row>
@@ -1081,11 +1105,11 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　３　身体障がい者の現状</t>
+          <t xml:space="preserve">　　２　障がい者手帳の所持者数</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
     </row>
@@ -1097,11 +1121,11 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　４　知的障がい者の現状</t>
+          <t xml:space="preserve">　　３　身体障がい者の現状</t>
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
     </row>
@@ -1113,11 +1137,11 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　５　精神障がい者の現状</t>
+          <t xml:space="preserve">　　４　知的障がい者の現状</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D18" s="5" t="inlineStr"/>
     </row>
@@ -1129,11 +1153,11 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　６　障がい者手帳所持者数の将来推計</t>
+          <t xml:space="preserve">　　５　精神障がい者の現状</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
     </row>
@@ -1145,7 +1169,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　７　障がい児の就学状況</t>
+          <t xml:space="preserve">　　６　障がい者手帳所持者数の将来推計</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
@@ -1161,49 +1185,49 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　７　障がい児の就学状況</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　８　アンケート調査の実施について</t>
         </is>
       </c>
-      <c r="C21" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="C22" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>第3章　計画の基本理念・基本目標及び施策体系</t>
         </is>
       </c>
-      <c r="C22" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="C23" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　１　基本理念</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1213,11 +1237,11 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　２　基本目標</t>
+          <t xml:space="preserve">　　１　基本理念</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D24" s="5" t="inlineStr"/>
     </row>
@@ -1229,11 +1253,11 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　３　施策体系と各施策の方向性</t>
+          <t xml:space="preserve">　　２　基本目標</t>
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
     </row>
@@ -1245,11 +1269,11 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　４　第８期計画で加わる視点と施策体系の対応</t>
+          <t xml:space="preserve">　　３　施策体系と各施策の方向性</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
     </row>
@@ -1261,7 +1285,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　５　第４次障がい者計画の目標値と進捗管理</t>
+          <t xml:space="preserve">　　４　第８期計画で加わる視点と施策体系の対応</t>
         </is>
       </c>
       <c r="C27" s="17" t="n">
@@ -1270,40 +1294,40 @@
       <c r="D27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　５　第４次障がい者計画の目標値と進捗管理</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>第4章　令和11年度に向けた成果目標</t>
         </is>
       </c>
-      <c r="C28" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="C29" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　（１）　福祉施設の入所者の地域生活への移行</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="D29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1313,11 +1337,11 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　（２）　精神障害にも対応した地域包括ケアシステムの構築</t>
+          <t xml:space="preserve">　　（１）　福祉施設の入所者の地域生活への移行</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" s="5" t="inlineStr"/>
     </row>
@@ -1329,7 +1353,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　（３）　福祉施設から一般就労への移行等</t>
+          <t xml:space="preserve">　　（２）　精神障害にも対応した地域包括ケアシステムの構築</t>
         </is>
       </c>
       <c r="C31" s="17" t="n">
@@ -1345,11 +1369,11 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　（４）　障がい児支援の提供体制の整備等</t>
+          <t xml:space="preserve">　　（３）　福祉施設から一般就労への移行等</t>
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D32" s="5" t="inlineStr"/>
     </row>
@@ -1361,11 +1385,11 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　（５）　地域生活支援の充実</t>
+          <t xml:space="preserve">　　（４）　障がい児支援の提供体制の整備等</t>
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D33" s="7" t="inlineStr"/>
     </row>
@@ -1377,11 +1401,11 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　（６）　相談支援体制の充実・強化等</t>
+          <t xml:space="preserve">　　（５）　地域生活支援の充実</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
     </row>
@@ -1393,11 +1417,11 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　（７）　障がい福祉人材の確保・定着及び当事者視点に立ったケアの充実のための生産性向上【新規】</t>
+          <t xml:space="preserve">　　（６）　相談支援体制の充実・強化等</t>
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
     </row>
@@ -1409,49 +1433,49 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　（７）　障がい福祉人材の確保・定着及び当事者視点に立ったケアの充実のための生産性向上【新規】</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　（８）　障がい福祉サービス等の質を向上させるための取組みに係る体制の構築</t>
         </is>
       </c>
-      <c r="C36" s="18" t="n">
-        <v>26</v>
-      </c>
-      <c r="D36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="C37" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>第5章　障がい福祉サービス等の実績と今後の見込み量</t>
         </is>
       </c>
-      <c r="C37" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="C38" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　１　見込量の推計方法</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="n">
-        <v>28</v>
-      </c>
-      <c r="D38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1461,11 +1485,11 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　２　年齢到達に伴うサービスの移行</t>
+          <t xml:space="preserve">　　１　見込量の推計方法</t>
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
     </row>
@@ -1477,11 +1501,11 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　３　訪問系サービス</t>
+          <t xml:space="preserve">　　２　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
     </row>
@@ -1493,11 +1517,11 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　４　日中活動系サービス</t>
+          <t xml:space="preserve">　　３　訪問系サービス</t>
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
     </row>
@@ -1509,7 +1533,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　５　居住系サービス</t>
+          <t xml:space="preserve">　　４　日中活動系サービス</t>
         </is>
       </c>
       <c r="C42" s="18" t="n">
@@ -1525,11 +1549,11 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　６　相談支援</t>
+          <t xml:space="preserve">　　５　居住系サービス</t>
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
     </row>
@@ -1541,11 +1565,11 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　７　障がい児支援</t>
+          <t xml:space="preserve">　　６　相談支援</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
     </row>
@@ -1557,11 +1581,11 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　８　必要な見込量の確保のための方策</t>
+          <t xml:space="preserve">　　７　障がい児支援</t>
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
     </row>
@@ -1573,7 +1597,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　９　地域生活支援事業の実施目標</t>
+          <t xml:space="preserve">　　８　必要な見込量の確保のための方策</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
@@ -1589,7 +1613,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　10　活動指標</t>
+          <t xml:space="preserve">　　９　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="C47" s="17" t="n">
@@ -1605,11 +1629,11 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　11　事業提供体制の確保のための方策</t>
+          <t xml:space="preserve">　　10　活動指標</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
     </row>
@@ -1621,49 +1645,49 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　11　事業提供体制の確保のための方策</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　12　障がい福祉サービス等に係る費用の推移と財源構成</t>
         </is>
       </c>
-      <c r="C49" s="17" t="n">
-        <v>47</v>
-      </c>
-      <c r="D49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+      <c r="C50" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="D50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>第6章　成年後見制度の利用促進</t>
         </is>
       </c>
-      <c r="C50" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="C51" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　１　現状と課題</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -1673,49 +1697,49 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　１　現状と課題</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　２　中核機関の設置</t>
         </is>
       </c>
-      <c r="C52" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="C53" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>第7章　他計画との連携</t>
         </is>
       </c>
-      <c r="C53" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="C54" s="16" t="n">
+        <v>53</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　１　第３次健康21・北塩原村グッドヘルスプランとの連携</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="n">
-        <v>51</v>
-      </c>
-      <c r="D54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -1725,11 +1749,11 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　２　北塩原村第五次総合振興計画との連携</t>
+          <t xml:space="preserve">　　１　第３次健康21・北塩原村グッドヘルスプランとの連携</t>
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
     </row>
@@ -1741,49 +1765,49 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　２　北塩原村第五次総合振興計画との連携</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>54</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　３　北塩原村こども・子育て計画との連携</t>
         </is>
       </c>
-      <c r="C56" s="18" t="n">
-        <v>53</v>
-      </c>
-      <c r="D56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="C57" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>第8章　資料編</t>
         </is>
       </c>
-      <c r="C57" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="C58" s="16" t="n">
+        <v>56</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　１　アンケート調査集計結果</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n">
-        <v>54</v>
-      </c>
-      <c r="D58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -1793,11 +1817,11 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　２　北塩原村障がい者自立支援協議会委員名簿</t>
+          <t xml:space="preserve">　　１　アンケート調査集計結果</t>
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
     </row>
@@ -1809,16 +1833,48 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　２　北塩原村障がい者自立支援協議会委員名簿</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>56</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　３　策定経過</t>
         </is>
       </c>
-      <c r="C60" s="18" t="n">
-        <v>54</v>
-      </c>
-      <c r="D60" s="5" t="inlineStr"/>
-    </row>
-    <row r="62" ht="52" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="C61" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　４　用語解説</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>56</v>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+    </row>
+    <row r="64" ht="52" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>目次に載せる階層は第2階層（章＋節）までとしています。本文には第3階層の小見出しが38件あり、3階層まで載せると93項目・約4ページとなり本文60ページに対して過大になるためです。現行計画の目次も章＋節の2階層でした。3階層に変えたい場合は build_kitashiobara_mokuji.py の TOC_LEVELS を3にします。</t>
         </is>
@@ -1827,8 +1883,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A64:D64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2014,7 +2070,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>施策体系は引き継いだが、ＳＤＧｓ17目標との対応が落ちている</t>
+          <t>施策体系は引き継いだが、ＳＤＧｓ17目標との対応が落ちている。令和8年9月16日、今回は追加しない方針を確認（G-3）</t>
         </is>
       </c>
     </row>
@@ -2154,17 +2210,17 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>欠落</t>
+          <t>第1章7 障がい福祉サービスの体系</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>サービスの全体像（介護給付・訓練等給付・相談支援・障害児支援・地域生活支援事業）を示す一覧が落ちている</t>
+          <t>令和8年9月16日に新設（30区分）。現行計画と同じ第1章の末尾に置いた。第5章の節番号は本文・管理ブックから25か所以上参照されており繰り下げの影響が大きいため</t>
         </is>
       </c>
     </row>
@@ -3054,17 +3110,17 @@
       <c r="C45" s="17" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>欠落</t>
+          <t>目次の後（前付け）</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>表記ルールの説明。概要版にも同じ注記がある</t>
+          <t>令和8年9月16日に追加。現行計画と同じ文言。概要版にも同じ注記がある</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3290,12 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>第5章の冒頭（第5章1 見込量の推計方法の前）に1頁で新設する。サービス見込量ブックの27サービス区分をそのまま使える</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>追加を推奨</t>
+          <t>現行計画と同じ第1章の末尾（第1章7）に新設した。30区分を区分・サービス名・内容の3列で示している。第5章の冒頭も考えられたが、第5章の節番号は本文・管理ブックから25か所以上参照されており、繰り下げの影響が大きいため第1章とした</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>反映済（第1章7）</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3327,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>目次の次頁または奥付前に、前回と同じ文言で置く</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>追加を推奨</t>
+          <t>目次の後（前付け・ノンブル対象外）に、現行計画と同じ文言で置いた</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>反映済（目次の後）</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3364,12 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>第3章3の施策体系表に、前回のＳＤＧｓ対応列をそのまま再掲する。1頁を要するため、分量配分（第3章6頁）との兼ね合いで村と相談する</t>
+          <t>第3章3の施策体系表に、前回のＳＤＧｓ対応列をそのまま再掲する。1頁を要するため、分量配分（第3章6頁）との兼ね合いで村と相談する。令和8年9月16日、今回は追加しない方針を確認</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>村と協議</t>
+          <t>今回は見送り</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3404,7 @@
           <t>現行の第3章3は施策体系と方向性を1節にまとめており、仕様書の記載事項は満たしている。前回13頁を再掲すると計画の重心がずれるため、分量配分計画のとおり第3章は6頁に抑える。詳細は第4次障がい者計画本体を参照する旨を注記する</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>現行のままでよい</t>
         </is>
@@ -3385,7 +3441,7 @@
           <t>今回の仕様書5の成果品は①計画書②アンケート調査報告書③電子媒体の3点で、概要版は含まれていない。村が前回同様に期待している可能性があるため、範囲・部数・費用を早期に確認する</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>村と協議（契約範囲）</t>
         </is>
@@ -3419,12 +3475,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>資料編（第8章）に1頁で新設する。アンケート調査票で村が指定した用語説明（レスパイトケア、就労継続支援Ａ型・Ｂ型）の文言をそのまま使える</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>追加を提案</t>
+          <t>資料編（第8章）に1頁で新設する。第8章4として新設した（30語）。本文に実際に現れる語に限り、個別のサービスの内容は第1章7の体系表に委ねて重複を避けている</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>反映済（第8章4）</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -65,7 +65,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -117,11 +117,6 @@
         <fgColor rgb="00808080"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007030A0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -149,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -206,9 +201,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -729,12 +721,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>計画書 A4両面 約60頁 30部</t>
+          <t>計画書 A4両面 約60頁 30部＋概要版 A4・4頁</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>概要版は今回の仕様書に含まれていない（G-5）</t>
+          <t>概要版は仕様書の成果品3点に含まれていないが、村の指示により作成（G-5）</t>
         </is>
       </c>
     </row>
@@ -834,7 +826,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
       <c r="D19" s="5" t="inlineStr">
@@ -850,7 +842,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="8" t="inlineStr"/>
       <c r="D20" s="7" t="inlineStr">
@@ -862,7 +854,7 @@
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>落ちていた4件のうち2件は令和8年9月16日に追加し（2件）、あわせて用語解説を新設しました。残る2件は、ＳＤＧｓ対応表（今回は見送り）と概要版（仕様書の成果品に含まれておらず契約範囲の確認が必要）です。第3章の施策の展開は改定対象外のため現行のままとしています。詳細は 03_不足分 をご覧ください。</t>
+          <t>落ちていた4件のうち3件を追加しました（3件）。令和8年9月16日にサービスの体系・表記の注記を追加して用語解説を新設し、同年9月17日に概要版を別ファイルで作成しています。残る1件はＳＤＧｓ対応表（今回は見送り）です。第3章の施策の展開は改定対象外のため現行のままとしています。詳細は 03_不足分 をご覧ください。</t>
         </is>
       </c>
     </row>
@@ -3168,17 +3160,17 @@
       <c r="C47" s="17" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>欠落</t>
+          <t>別冊 北塩原村_計画素案_概要版.docx（A4・4頁）</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>前回は概要版を作成していたが、今回の仕様書5の成果品は①計画書②アンケート調査報告書③電子媒体の3点で概要版が含まれていない</t>
+          <t>令和8年9月17日に村の指示により作成。仕様書5の成果品3点には含まれていないため、契約上の取扱い（部数・費用）は別途村と整理する</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3430,12 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>今回の仕様書5の成果品は①計画書②アンケート調査報告書③電子媒体の3点で、概要版は含まれていない。村が前回同様に期待している可能性があるため、範囲・部数・費用を早期に確認する</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>村と協議（契約範囲）</t>
+          <t>令和8年9月17日、村の指示により別ファイルで作成した（build_kitashiobara_gaiyou.py → 北塩原村_計画素案_概要版.docx）。前回の構成を踏襲しつつ、改定対象外の障がい者計画は「継承する内容」として整理し、ＳＤＧｓの節は国の基本指針の見直しのポイントに差し替えた。仕様書5の成果品3点には含まれていないため、部数・費用の扱いは別途村と整理する</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>反映済（別冊・概要版）</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>49節</t>
+          <t>51節</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>56頁（推定）</t>
+          <t>60頁（推定）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -888,7 +888,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案の目次（57項目・推定56ページ）</t>
+          <t>計画素案の目次（59項目・推定60ページ）</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D32" s="5" t="inlineStr"/>
     </row>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33" s="7" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
     </row>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
     </row>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
     </row>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="C38" s="16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
     </row>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
     </row>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
     </row>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
     </row>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
     </row>
@@ -1657,29 +1657,25 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>第6章　成年後見制度の利用促進</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="n">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　13　障がい福祉人材の確保・定着、生産性向上及び経営基盤の確立</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="n">
         <v>52</v>
       </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>章</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -1689,49 +1685,49 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　14　関係機関との連携</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>53</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>第6章　成年後見制度の利用促進</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>56</v>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　１　現状と課題</t>
         </is>
       </c>
-      <c r="C52" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="D52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　２　中核機関の設置</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="n">
-        <v>52</v>
-      </c>
-      <c r="D53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>第7章　他計画との連携</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>章</t>
-        </is>
-      </c>
+      <c r="C54" s="18" t="n">
+        <v>56</v>
+      </c>
+      <c r="D54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -1741,29 +1737,33 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　１　第３次健康21・北塩原村グッドヘルスプランとの連携</t>
+          <t xml:space="preserve">　　２　中核機関の設置</t>
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　２　北塩原村第五次総合振興計画との連携</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="n">
-        <v>54</v>
-      </c>
-      <c r="D56" s="5" t="inlineStr"/>
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>第7章　他計画との連携</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -1773,33 +1773,29 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　３　北塩原村こども・子育て計画との連携</t>
+          <t xml:space="preserve">　　１　第３次健康21・北塩原村グッドヘルスプランとの連携</t>
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>第8章　資料編</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>章</t>
-        </is>
-      </c>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　２　北塩原村第五次総合振興計画との連携</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>58</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -1809,29 +1805,33 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　１　アンケート調査集計結果</t>
+          <t xml:space="preserve">　　３　北塩原村こども・子育て計画との連携</t>
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　２　北塩原村障がい者自立支援協議会委員名簿</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n">
-        <v>56</v>
-      </c>
-      <c r="D60" s="5" t="inlineStr"/>
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>第8章　資料編</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -1841,11 +1841,11 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　３　策定経過</t>
+          <t xml:space="preserve">　　１　アンケート調査集計結果</t>
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
     </row>
@@ -1857,16 +1857,48 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　２　北塩原村障がい者自立支援協議会委員名簿</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　３　策定経過</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　４　用語解説</t>
         </is>
       </c>
-      <c r="C62" s="18" t="n">
-        <v>56</v>
-      </c>
-      <c r="D62" s="5" t="inlineStr"/>
-    </row>
-    <row r="64" ht="52" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="C64" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="52" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>目次に載せる階層は第2階層（章＋節）までとしています。本文には第3階層の小見出しが38件あり、3階層まで載せると93項目・約4ページとなり本文60ページに対して過大になるためです。現行計画の目次も章＋節の2階層でした。3階層に変えたい場合は build_kitashiobara_mokuji.py の TOC_LEVELS を3にします。</t>
         </is>
@@ -1875,8 +1907,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A66:D66"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A64:D64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>60頁（推定）</t>
+          <t>64頁（推定）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案の目次（59項目・推定60ページ）</t>
+          <t>計画素案の目次（59項目・推定64ページ）</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D24" s="5" t="inlineStr"/>
     </row>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
     </row>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
     </row>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D27" s="7" t="inlineStr"/>
     </row>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
     </row>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D30" s="5" t="inlineStr"/>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D32" s="5" t="inlineStr"/>
     </row>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D33" s="7" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
     </row>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
     </row>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
     </row>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="C38" s="16" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
     </row>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
     </row>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
     </row>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
     </row>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
     </row>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
     </row>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
     </row>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
     </row>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
     </row>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
     </row>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
     </row>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>64頁（推定）</t>
+          <t>65頁（推定）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案の目次（59項目・推定64ページ）</t>
+          <t>計画素案の目次（59項目・推定65ページ）</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
     </row>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
     </row>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
     </row>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
     </row>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
     </row>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
     </row>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
     </row>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
     </row>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
     </row>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
     </row>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
     </row>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>65頁（推定）</t>
+          <t>69頁（推定）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案の目次（59項目・推定65ページ）</t>
+          <t>計画素案の目次（59項目・推定69ページ）</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
     </row>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
     </row>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
     </row>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
     </row>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D18" s="5" t="inlineStr"/>
     </row>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
     </row>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
     </row>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
     </row>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
     </row>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D24" s="5" t="inlineStr"/>
     </row>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
     </row>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
     </row>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D27" s="7" t="inlineStr"/>
     </row>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
     </row>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D30" s="5" t="inlineStr"/>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D32" s="5" t="inlineStr"/>
     </row>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D33" s="7" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
     </row>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
     </row>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
     </row>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="C38" s="16" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
     </row>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
     </row>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
     </row>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
     </row>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
     </row>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
     </row>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
     </row>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
     </row>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
     </row>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
     </row>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
     </row>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>69頁（推定）</t>
+          <t>71頁（推定）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案の目次（59項目・推定69ページ）</t>
+          <t>計画素案の目次（59項目・推定71ページ）</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
     </row>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
     </row>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
     </row>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="C38" s="16" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
     </row>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
     </row>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
     </row>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
     </row>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
     </row>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
     </row>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
     </row>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
     </row>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
     </row>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
     </row>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
     </row>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>71頁（推定）</t>
+          <t>73頁（推定）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案の目次（59項目・推定71ページ）</t>
+          <t>計画素案の目次（59項目・推定73ページ）</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
     </row>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
     </row>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
     </row>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
     </row>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D18" s="5" t="inlineStr"/>
     </row>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
     </row>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
     </row>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
     </row>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
     </row>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D24" s="5" t="inlineStr"/>
     </row>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
     </row>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
     </row>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D27" s="7" t="inlineStr"/>
     </row>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
     </row>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D30" s="5" t="inlineStr"/>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D32" s="5" t="inlineStr"/>
     </row>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D33" s="7" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
     </row>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
     </row>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
     </row>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="C38" s="16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
     </row>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
     </row>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
     </row>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
     </row>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
     </row>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
     </row>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
     </row>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
     </row>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
     </row>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
     </row>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
     </row>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>73頁（推定）</t>
+          <t>77頁（推定）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案の目次（59項目・推定73ページ）</t>
+          <t>計画素案の目次（59項目・推定77ページ）</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
     </row>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
     </row>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
     </row>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
     </row>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
     </row>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
     </row>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
     </row>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
     </row>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
     </row>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
     </row>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
     </row>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>51節</t>
+          <t>52節</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>77頁（推定）</t>
+          <t>82頁（推定）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -888,7 +888,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案の目次（59項目・推定77ページ）</t>
+          <t>計画素案の目次（60項目・推定82ページ）</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
     </row>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
     </row>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
     </row>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="C38" s="16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
     </row>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
     </row>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
     </row>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
     </row>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
     </row>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
     </row>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
     </row>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
     </row>
@@ -1741,45 +1741,45 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　３　制度の見直しへの対応</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>第7章　他計画との連携</t>
         </is>
       </c>
-      <c r="C56" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="C57" s="16" t="n">
+        <v>79</v>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　１　第３次健康21・北塩原村グッドヘルスプランとの連携</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="n">
-        <v>74</v>
-      </c>
-      <c r="D57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -1789,11 +1789,11 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　２　北塩原村第五次総合振興計画との連携</t>
+          <t xml:space="preserve">　　１　第３次健康21・北塩原村グッドヘルスプランとの連携</t>
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
     </row>
@@ -1805,49 +1805,49 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　２　北塩原村第五次総合振興計画との連携</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　３　北塩原村こども・子育て計画との連携</t>
         </is>
       </c>
-      <c r="C59" s="17" t="n">
-        <v>76</v>
-      </c>
-      <c r="D59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
+      <c r="C60" s="18" t="n">
+        <v>81</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>第8章　資料編</t>
         </is>
       </c>
-      <c r="C60" s="16" t="n">
-        <v>77</v>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="C61" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　１　アンケート調査集計結果</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="n">
-        <v>77</v>
-      </c>
-      <c r="D61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -1857,11 +1857,11 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　２　北塩原村障がい者自立支援協議会委員名簿</t>
+          <t xml:space="preserve">　　１　アンケート調査集計結果</t>
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
     </row>
@@ -1873,11 +1873,11 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　３　策定経過</t>
+          <t xml:space="preserve">　　２　北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
     </row>
@@ -1889,16 +1889,32 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　３　策定経過</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　４　用語解説</t>
         </is>
       </c>
-      <c r="C64" s="18" t="n">
-        <v>77</v>
-      </c>
-      <c r="D64" s="5" t="inlineStr"/>
-    </row>
-    <row r="66" ht="52" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="C65" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr"/>
+    </row>
+    <row r="67" ht="52" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>目次に載せる階層は第2階層（章＋節）までとしています。本文には第3階層の小見出しが38件あり、3階層まで載せると93項目・約4ページとなり本文60ページに対して過大になるためです。現行計画の目次も章＋節の2階層でした。3階層に変えたい場合は build_kitashiobara_mokuji.py の TOC_LEVELS を3にします。</t>
         </is>
@@ -1907,7 +1923,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A67:D67"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
     </row>

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -3208,7 +3208,7 @@
       <c r="C47" s="17" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>別冊 北塩原村_計画素案_概要版.docx（A4・4頁）</t>
+          <t>別冊 北塩原村_計画素案_概要版.docx（A4・7頁）</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月17日に村の指示により作成。仕様書5の成果品3点には含まれていないため、契約上の取扱い（部数・費用）は別途村と整理する</t>
+          <t>令和8年9月17日に村の指示により作成。前回は4頁であったが、令和8年10月10日に正本の3節（方策・年齢到達・他計画との連携）を受けて6頁、令和8年10月14日に体系の折衷案（案Ｃ）により節8「本計画で新たに加える施策」を加えて7頁とした。仕様書5の成果品3点には含まれていないため、契約上の取扱い（部数・費用）は別途村と整理する</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月17日、村の指示により別ファイルで作成した（build_kitashiobara_gaiyou.py → 北塩原村_計画素案_概要版.docx）。前回の構成を踏襲しつつ、改定対象外の障がい者計画は「継承する内容」として整理し、ＳＤＧｓの節は国の基本指針の見直しのポイントに差し替えた。仕様書5の成果品3点には含まれていないため、部数・費用の扱いは別途村と整理する</t>
+          <t>令和8年9月17日、村の指示により別ファイルで作成した（build_kitashiobara_gaiyou.py → 北塩原村_計画素案_概要版.docx）。前回の構成を踏襲しつつ、改定対象外の障がい者計画は「継承する内容」として整理し、ＳＤＧｓの節は国の基本指針の見直しのポイントに差し替えた。令和8年10月14日に、体系の折衷案（案Ｃ）の採用に伴い節8「本計画で新たに加える施策」（正本 表３-３と同じ15件）を加え、今後の予定をパブリックコメントの日付入りに改めて7頁とした。仕様書5の成果品3点には含まれていないため、部数・費用の扱いは別途村と整理する</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">

--- a/output/北塩原村_目次構成_前回対比.xlsx
+++ b/output/北塩原村_目次構成_前回対比.xlsx
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月17日、村の指示により別ファイルで作成した（build_kitashiobara_gaiyou.py → 北塩原村_計画素案_概要版.docx）。前回の構成を踏襲しつつ、改定対象外の障がい者計画は「継承する内容」として整理し、ＳＤＧｓの節は国の基本指針の見直しのポイントに差し替えた。令和8年10月14日に、体系の折衷案（案Ｃ）の採用に伴い節8「本計画で新たに加える施策」（正本 表３-３と同じ15件）を加え、今後の予定をパブリックコメントの日付入りに改めて7頁とした。仕様書5の成果品3点には含まれていないため、部数・費用の扱いは別途村と整理する</t>
+          <t>令和8年9月17日、村の指示により別ファイルで作成した（build_kitashiobara_gaiyou.py → 北塩原村_計画素案_概要版.docx）。前回の構成を踏襲しつつ、改定対象外の障がい者計画は「継承する内容」として整理し、ＳＤＧｓの節は国の基本指針の見直しのポイントに差し替えた。令和8年10月14日に、体系の折衷案（案Ｃ）の採用に伴い節8「本計画で新たに加える施策」（正本 表３-３と同じ15件）を加え、今後の予定をパブリックコメントの日付入りに改めて7頁とした。あわせて、前回計画の評価（Ａ４・2頁）とアンケート結果報告（Ａ４・2頁）の概要版を作成し、3本を本体と概要版でそろえた（build_kitashiobara_gaiyou_2hon.py）。仕様書5の成果品3点には含まれていないため、部数・費用の扱いは別途村と整理する</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
